--- a/光伏配储项目/电价数据/2026/菩堤升压站.xlsx
+++ b/光伏配储项目/电价数据/2026/菩堤升压站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51057</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38555</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.73678</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.57096</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.56701</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.49377</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43767</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.4545</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43874</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42313</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42029</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.4089</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39821</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.3998</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40203</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35458</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39158</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41704</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.3921</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42072</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42399</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41291</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44397</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35683</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33703</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.27852</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30646</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.10919</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.08940000000000001</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.09409999999999999</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.07926000000000001</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.1025</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.08181000000000001</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.09689</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.09317</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.07389</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08929000000000001</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.07176</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.05477000000000001</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.01749</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14813</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21471</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.24228</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.26292</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.19353</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.07532999999999999</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.00198</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.27131</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.14582</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.26083</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.27506</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.17772</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.49735</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.33798</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.44065</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.73649</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.38931</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.5609299999999999</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.4241</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44911</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.41217</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.55983</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.42911</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.5791900000000001</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.78859</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.6323799999999999</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.5992999999999999</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.6922</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.7466699999999999</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.64624</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.57997</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.6089199999999999</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.56198</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.54902</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.6265499999999999</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.5957</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.4618</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48653</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.43357</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.67761</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.49164</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.74314</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.11357</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.52615</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5206900000000001</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5064</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50757</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49247</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47163</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39205</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37124</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35966</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37602</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37602</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42057</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.5022099999999999</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.5968600000000001</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.67541</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.43088</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.36205</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.40548</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.49499</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.13924</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.02281</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.31349</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.33431</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.32068</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.43965</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.6870299999999999</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.79486</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.31221</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.34444</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.70385</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.47597</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.07127</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.27576</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.30325</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.30299</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.30324</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.44336</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.30097</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.22394</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.30252</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.29863</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.24194</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.24592</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.44648</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.40408</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.28753</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.5069</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.6273</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.47814</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.6809700000000001</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.7426799999999999</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.7448899999999999</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.47414</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.46915</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.78244</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.54477</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.39519</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.83497</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.45106</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.5892500000000001</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.4401</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43373</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33631</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5137</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48417</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35639</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.37245</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.36337</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47387</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44431</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35387</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35172</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.1931</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.37467</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.30264</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.39465</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.48737</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.36963</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.1321</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.28542</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.23312</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.28477</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.26534</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.27127</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.37608</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.37307</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.41309</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.38906</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.4207</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.39794</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.42401</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.50917</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.36876</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.44431</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.57713</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.32701</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.4303</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.38782</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.41497</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.44431</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.4303</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.38124</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.38696</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.38921</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.3432</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.37095</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.39703</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.35648</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.36229</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.34317</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.35254</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46103</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.30964</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.30907</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.30606</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.30897</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33826</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.35921</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.33566</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.33774</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.2843</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26873</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.29186</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.19501</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.14875</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.3135</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.2461</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.21021</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.48748</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.30452</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.40399</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.3003</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.12545</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.28921</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.27737</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.14093</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.46965</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.10307</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.19426</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.21881</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.38564</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.34805</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.30479</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.22569</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.24447</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.21336</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.26901</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.1456</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.25768</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.27848</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.30207</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.33241</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.41788</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.56176</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.45263</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.43984</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.36597</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.35057</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.35673</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.36657</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.30603</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.3001</v>
+      </c>
+      <c r="D121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="G121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="S121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30698</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21904</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.0444</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.10314</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.2901</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38596</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.3923</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38596</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37906</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.3413</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.4027</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41717</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46752</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41614</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34681</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.351</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.6687000000000001</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44602</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35898</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33411</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.3001</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.1025</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.09831000000000001</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14031</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36593</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33587</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31995</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.3102</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40508</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32022</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31423</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.3004</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.16984</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15646</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1686</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14582</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15718</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15646</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.2327</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.2119</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22474</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.2797</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.2697</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.43779</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.48234</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.42665</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40799</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15669</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50763</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62201</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49794</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78099</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92031</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.4945</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.92111</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8842300000000001</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.30778</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.37476</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.9084500000000001</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63524</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.2077</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.55935</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.35195</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.04742</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.55191</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.80889</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5303</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7918200000000001</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87899</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.88327</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50997</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41511</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.42117</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.46899</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.22828</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87899</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5511200000000001</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6430800000000001</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54344</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50364</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45824</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42659</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44074</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45075</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39343</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45275</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42087</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36523</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.39062</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41476</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39065</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.35214</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35639</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40781</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.4508</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58761</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42768</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59596</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.6017100000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6690700000000001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46542</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.59373</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.87387</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.5970700000000001</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8549600000000001</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.83793</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.86798</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.43935</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.3303</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.45275</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.2952</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.3303</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30823</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.30284</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.3233</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45236</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.354</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.93132</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.47063</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.37777</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.4436</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.50008</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38934</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.4104</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.37409</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.38833</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.36563</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33794</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16551</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30842</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.32984</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.20959</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.34167</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31247</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29292</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25559</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.34824</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.2801</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32897</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38552</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43583</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.3239</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35134</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44849</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32547</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.4204</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40168</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59663</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.34277</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.1436</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70025</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.65188</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5809500000000001</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43956</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43711</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41476</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.3902</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42768</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39608</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.44635</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29441</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30842</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33378</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30178</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.2501</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.5157</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.29244</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.29793</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.36448</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.36786</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.29906</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.2392</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.2793</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28312</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29285</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.34374</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.1788</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.16469</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.14404</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.20452</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.17664</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.16459</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.1598</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.15484</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.1447</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.08778</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.06570000000000001</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.09668</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.09813</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.05528</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.07329000000000001</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.03496</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.04577000000000001</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.13765</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.17105</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.18242</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.17609</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.20228</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.16727</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.20781</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.20259</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.18669</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.22129</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.18962</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.23792</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.20116</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.2239</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.28725</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.243</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.24217</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.25643</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.28087</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.27799</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.28206</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.27553</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.243</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.2315</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.23829</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.23291</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.1971</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.20315</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.18717</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.20721</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.26026</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.25528</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.2064</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.282</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.28555</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.29538</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.2336</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.24312</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.22506</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.20721</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.20721</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.20721</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.26844</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.2859</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.2703</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.22877</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.15698</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.26752</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.15849</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.29558</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.1578</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.07726000000000001</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.19719</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.12567</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.21071</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.15567</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.25755</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.21771</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.13153</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.25589</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.26714</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.30573</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.16684</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.24265</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.20537</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.26423</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.27169</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.27284</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.2783</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.26709</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.27914</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33412</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.29306</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.31736</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.27554</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.32384</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.30131</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.34643</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.1713</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.15321</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.20526</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.14129</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.33478</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.22517</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.24307</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.29064</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.30012</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.35706</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.21257</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.30001</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.29159</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.20234</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.2878</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.2859</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.28869</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.28117</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.28264</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.27927</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.27905</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.20721</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.27169</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.28211</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.27346</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.21084</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.22318</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.27169</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.26695</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.26222</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.2752</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.26419</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.26506</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.32751</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.24327</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.27987</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.19084</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.37138</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.24327</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.23379</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.31785</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.21958</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.19589</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.21958</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.04759</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.24081</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.25937</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.23379</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.21958</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.18171</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.18486</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.19322</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.13812</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.25748</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.28969</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.20067</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.25674</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.2423</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.14612</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.13606</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.14079</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.1877</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.16075</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.18803</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.19256</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.19712</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.20202</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.14907</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.1486</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.30953</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.25152</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.21778</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.17711</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.12919</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.13352</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.14183</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.29755</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.22202</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.23442</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.17707</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.19421</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.19858</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.19708</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.11138</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.02864</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.17869</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.16777</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.12307</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.16137</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.19195</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.03836999999999999</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.26506</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.19491</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.19578</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.19447</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.26819</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.26506</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.27169</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.19375</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.26222</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.2625</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.26506</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.26819</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.27169</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.27643</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.2878</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.28117</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.28117</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.27614</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.27927</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.26243</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.26222</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.2752</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.28488</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.28969</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.27643</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.26819</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.26231</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.18926</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.19312</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.25937</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.2859</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.1886</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.29064</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.2893</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.18964</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.27485</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.23034</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.26819</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.26072</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.19277</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.26819</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.27018</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.2770899999999999</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.2954</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.2697</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.26222</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.26222</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.26222</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.25682</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.29064</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.25303</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.24924</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.2893</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.30012</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.28234</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.29064</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.30021</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.27255</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.27169</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.2135</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.31433</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.30021</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.30675</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.3238</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.29532</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.30959</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.29064</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.21619</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.29064</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.31769</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.32316</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.21297</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.21297</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33868</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33701</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.20834</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.20133</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.19788</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.19167</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.27507</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.26061</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.27008</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.18485</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.27573</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.26279</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.2683</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.27435</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.24247</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.2796</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.27222</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.27211</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.24295</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.24338</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.05431</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36669</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.24185</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.36479</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.25386</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.53626</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.19853</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.26118</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.29911</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.21563</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.21397</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.345</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.16272</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.21229</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.21101</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.20004</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.20126</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.20425</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.2026</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.20231</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.19895</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.19483</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.20162</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.20691</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.20117</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.20239</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.20239</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.22129</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.22129</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.19294</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.17404</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.16459</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.17732</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.16828</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.11147</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.14569</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.1264</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.04882</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.12525</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.08776</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.09234999999999999</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.03335</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.09068999999999999</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.11945</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.11267</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.12122</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.11945</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.13676</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.11824</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.13632</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.09097</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.00645</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.04048</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.04487</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.08721</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.10517</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.08676</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.09189</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.11945</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.11945</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.11945</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.20041</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.19665</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.15738</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.26222</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.2192</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.25678</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.40924</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.30086</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.28712</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.31453</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.32975</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.24607</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.21354</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.20041</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.26646</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.25678</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.21428</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.20241</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.4065</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.4065</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.25678</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.23799</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.24987</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.25763</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.24076</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.23735</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.24987</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.24964</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.2285</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.2285</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.23074</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.23431</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.23799</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.25214</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.24019</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.28744</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.28705</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.38345</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.28517</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.28754</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.2925</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.21978</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.22129</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.28526</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.22982</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.19889</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.17552</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.20216</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.21199</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.20823</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.19297</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.17006</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.15571</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.13111</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.17653</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.19288</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.19953</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.27917</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.19205</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.15669</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.14798</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.15757</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.15828</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.13287</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.15744</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.15433</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.17018</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.11945</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.1832</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.17614</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.19671</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.20272</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.18857</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.25875</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.28744</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.34415</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.55799</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.5166900000000001</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.5284500000000001</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.36859</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.33534</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.5396799999999999</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.60022</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.4631</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.50148</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.37592</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.305</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.29568</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.27532</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.28664</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.2358</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.29689</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.24019</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.2598</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.22281</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.20247</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.2118</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.20733</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.20887</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.22211</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.21571</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.21746</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.20386</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.22129</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.24019</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.23263</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.2149</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.20737</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.18286</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.1937</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.16884</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.16258</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.17728</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.18286</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.19732</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.15406</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.18082</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.12472</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.17917</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.12212</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.17613</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.2572</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.20905</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.27098</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.1454</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.13337</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.13163</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.12538</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.14265</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.17903</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.18606</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.00183</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.20404</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.22774</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.18083</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.27004</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.30427</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.28487</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.26946</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.25275</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.24188</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.24786</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.24273</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.25407</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.24238</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.22094</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.24966</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.3363</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.17499</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.24588</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.28436</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.25556</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.33762</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.2404</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.24839</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.20334</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.21986</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.20622</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.22462</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.17352</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.17849</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.17499</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.17849</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.17849</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.17876</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.18315</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.16919</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.17295</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.24037</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.21183</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.16233</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.16212</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.16258</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.17452</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.11551</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.1604</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.15191</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.06892</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.11848</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.04454</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.06806</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.08613</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.06165</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.14855</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.12424</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.0798</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.01094</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.07026</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.13361</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.13795</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.07031999999999999</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.09046</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.11229</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.09272</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.11552</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.12009</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.13818</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.16689</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.15826</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.15679</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.18071</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.1982</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.20761</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.22977</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.20909</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.21604</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.17012</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.21904</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.26916</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.34388</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.31392</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.18315</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.2259</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.24138</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.2236</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.31505</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.31505</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.29064</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.21799</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.213</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.17849</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.2175</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.16974</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.16043</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.1529</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.16463</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.16151</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.13347</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.13944</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.15524</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.15372</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.10951</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.10349</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.11684</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.00675</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.12583</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.13534</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.13559</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.16628</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.07271</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.06817000000000001</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.03842</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>-0.02188</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>-0.01003</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.04058</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.12782</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>-0.0386</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.02035</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.17903</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.15293</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.14042</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.06520000000000001</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.06937</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.1016</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.08129</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.06919</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.06793</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.15731</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.14002</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.14405</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.12312</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.0815</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.07158</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.15717</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.14199</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.16855</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.21138</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.19689</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.16362</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.15052</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.11681</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.15211</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.1192</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>-0.02616</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.26578</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.00674</v>
+      </c>
+      <c r="H137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.0413</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.009519999999999999</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.00413</v>
+      </c>
+      <c r="M137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N137" t="n">
+        <v>-0.00013</v>
+      </c>
+      <c r="O137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>-0.01575</v>
+      </c>
+      <c r="R137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.00378</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.0186</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.02884</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.05479999999999999</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.08735</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.0983</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.1471</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.02514</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.00821</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.02443</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.21169</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>-0.03932</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.01201</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.0288</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.18673</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>-0.0211</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.12549</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.12162</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.21484</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.23708</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.15851</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.27917</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.21044</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.2573</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.21425</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.04284</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.29594</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.29093</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.30514</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.28443</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.30078</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.30514</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.29538</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.3004</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.29254</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.31035</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.29235</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.30078</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.30959</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.27264</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.27454</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.27169</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.27264</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.27169</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.20721</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.26695</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.27179</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.29566</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.30959</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.21703</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.28117</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.21083</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K138" t="n">
+        <v>-0.04613</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N138" t="n">
+        <v>-0.03015</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.26355</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.00088</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.00012</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.2515</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.26695</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.25902</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.27141</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.26695</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.18123</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.26885</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.22366</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.28183</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.38618</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.29741</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.25148</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.25499</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.13244</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.24523</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.14713</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.29064</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.29733</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.30415</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.28116</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.18749</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.16768</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.16561</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.27305</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.11945</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.14466</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.15436</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.11606</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.18381</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.08069</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.05343</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.06545999999999999</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.15502</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.14692</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.16356</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.07862000000000001</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.14107</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.10577</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.13923</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.16214</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.11945</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.15715</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.27491</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.28385</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.23708</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.21701</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.27935</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.19963</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.20843</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.1573</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.26818</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.29408</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.24237</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.26393</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.16863</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.3303</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.03468</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.34842</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.19453</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.2796</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.30684</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.28578</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.2874</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.28063</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.29964</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.27564</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.22823</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.27362</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.24421</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.19353</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.27264</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.26894</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.28957</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.27264</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.27264</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.25867</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.26231</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.24537</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.27074</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.27236</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.27085</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.25865</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.2859</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.16053</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.21381</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.27731</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.27717</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.18926</v>
+      </c>
+      <c r="T139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.19734</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.21286</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.27264</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.28117</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.19199</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.23325</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.29538</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.30864</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.22439</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.29648</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.20549</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.27169</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.29064</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.30427</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.43597</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.41682</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.2961</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.29307</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.21911</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.21722</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.19857</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.07215000000000001</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.16553</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.24812</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.1815</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.20114</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.18815</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.15059</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.05586</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.17677</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.1678</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.05149</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.18326</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.18892</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.19131</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.16932</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.16716</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.14489</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.17247</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.1728</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.13808</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.17804</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.24807</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.15758</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.10901</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.05236</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.27117</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.11623</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.05213</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.18268</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.3928</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.30669</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.00215</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.06473999999999999</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>-0.01592</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.31515</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.36614</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.23185</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.2135</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.32308</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.30012</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.31324</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.30838</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.30636</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.30118</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.30012</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.31945</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.29325</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.26095</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.3003</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.21142</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.21491</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.25524</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.23812</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.30757</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.20196</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.19914</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.30885</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.31232</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.21471</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.22984</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.27189</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.25647</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.22589</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.1976</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.13799</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.25631</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.21268</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.18642</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.16159</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.20494</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.2149</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.22098</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.19328</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.16328</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.17144</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.15982</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.22165</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.21147</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.22127</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.25216</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.36143</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.4045</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.4047</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.35303</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.3853</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.11248</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.14399</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.26972</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.38517</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.34814</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.52237</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.57712</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.41513</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.38141</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.22056</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.23917</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.15418</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.20603</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.21155</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.18096</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.18451</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.18968</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.14845</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.18722</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.1753</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.11348</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.14493</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.17987</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.13782</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.05054</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.12508</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.10566</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.14482</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.19001</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.19366</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.21774</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.17316</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.16438</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.10549</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.0968</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.16101</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.15105</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.1444</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.13114</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.14863</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.08192000000000001</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.09595999999999999</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.03773</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.12081</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.12984</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>-0.02536</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.00771</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>-0.00641</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>-0.00271</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.10027</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.14747</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>-0.01168</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.03971</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.12597</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.07438</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>-0.00664</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>-0.00675</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>-0.005019999999999999</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.01934</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.00028</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>-0.0046</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.05889</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.11377</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.13306</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.07646</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.05099</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.28117</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.18125</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.1971</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.18482</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.19916</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.08003</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.17483</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.20239</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.22013</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.13107</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.22939</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.20587</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.16346</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.22824</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.23044</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.25764</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.22756</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.19885</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.21785</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.24147</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.22412</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.24076</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.19806</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.19636</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.19158</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.10884</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.30414</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.04072</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.2388</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.08316</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.0645</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.0376</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.04208</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.06843</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.11479</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.11566</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.04563</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.04293</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.09079999999999999</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.11412</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.14928</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.1504</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.11494</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.12767</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.03552</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.09431999999999999</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.10886</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.07345</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.04929</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.1227</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.0562</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.15104</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.05114</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.17946</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.07191</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>-0.01064</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.03538</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.05612</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.08056000000000001</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.09701</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.14836</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.14812</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.04769</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.04432</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.05529999999999999</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.04867</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.01984</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>-0.03247999999999999</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>-0.03251</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>-0.03251</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>-0.00675</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>-0.03251</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>-0.03251</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>-0.00675</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>-0.03251</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>-0.03251</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>-0.03251</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.02699</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.05354</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>-0.00675</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.01762</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>-0.02626</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.09487000000000001</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.13113</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.09414</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.08652</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.09254999999999999</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.05989</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.09437999999999999</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.23799</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.19295</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.20562</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.21039</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.13473</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.1706</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.21527</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.19578</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.1837</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.20373</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.18069</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.21288</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.18041</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.22677</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.21807</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.21664</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.20503</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.20931</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.21063</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.14069</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.18038</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.23831</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.19731</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.20182</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.18456</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.17658</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.11412</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.15956</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.09936</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.17896</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.09963</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.16625</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.10033</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.09470999999999999</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.07898000000000001</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.14551</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.09164</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.09090999999999999</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.17495</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.09673000000000001</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.10544</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.16524</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.10549</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.10112</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.08631</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.08292000000000001</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.009509999999999999</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.004059999999999999</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>-0.02676</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>-0.02028</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.00104</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>-0.02106</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>-0.04774</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.02365</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>-0.04332</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>-0.03573</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>-0.0381</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>-0.00675</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>-0.03454</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>-0.03497</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>-0.02203</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>-0.01987</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.00495</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.01486</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.07948999999999999</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.08508</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.10852</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.04512</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.10852</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.13535</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.1643</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.14741</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.09877</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.12508</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.07704999999999999</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.07765999999999999</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.18298</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.10721</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.10847</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.1493</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.22832</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.2186</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.15188</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.17037</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.22175</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.19395</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.22031</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.20132</v>
       </c>
     </row>
   </sheetData>
